--- a/human_resources_forms/030_employee_guarantee_assessment--human_resources_forms.xlsx
+++ b/human_resources_forms/030_employee_guarantee_assessment--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,8 +919,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'leave_of_absence'}</t>
+          <t>leave_of_absence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Leave of Absence'}</t>
+          <t>Leave of Absence</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'job_title'}</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Job Title'}</t>
+          <t>Job Title</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'job_responsibilities'}</t>
+          <t>job_responsibilities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Job Responsibilities'}</t>
+          <t>Job Responsibilities</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'regular_full-time'}</t>
+          <t>regular_full-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Regular Full-time'}</t>
+          <t>Regular Full-time</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'regular_part-time'}</t>
+          <t>regular_part-time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Regular Part-time'}</t>
+          <t>Regular Part-time</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'temp_full-time'}</t>
+          <t>temp_full-time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Temp Full-time'}</t>
+          <t>Temp Full-time</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'temp_part-time'}</t>
+          <t>temp_part-time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Temp Part-time'}</t>
+          <t>Temp Part-time</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
